--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2023_arica_y_parinacota.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 20:30</t>
+    <t xml:space="preserve">2026-08-02 20:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2023_arica_y_parinacota.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 11:02</t>
+    <t xml:space="preserve">2026-08-16 10:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2023_arica_y_parinacota.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 10:09</t>
+    <t xml:space="preserve">2026-08-19 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2023_arica_y_parinacota.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:02</t>
+    <t xml:space="preserve">2026-08-28 12:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2023_arica_y_parinacota.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 12:27</t>
+    <t xml:space="preserve">2026-09-06 17:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
